--- a/public/templates/000_pm_suite/01_프로젝트 관리/08_위험관리/프로젝트명_위험관리대장_V1.0_20230530.xlsx
+++ b/public/templates/000_pm_suite/01_프로젝트 관리/08_위험관리/프로젝트명_위험관리대장_V1.0_20230530.xlsx
@@ -521,7 +521,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[PM-26] SyncGuard AI 프로젝트 위험관리대장 (Risk Register) — 주식회사 한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>[PM-26] SyncFlow AI 프로젝트 위험관리대장 (Risk Register) — 주식회사 한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>화장품 상세페이지의 캘리그라피·그라데이션 배경 문구 OCR 오인식 위험</t>
+          <t>전장부품 기술시방서의 캘리그라피·그라데이션 배경 조항 OCR 오인식 위험</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>Upstage Document Parse + Clova OCR 듀얼 검증 및 FO 화면 내 바운딩박스 인라인 교정 UI 제공</t>
+          <t>EnterpriseVision Document Parse + Enterprise Vision OCR 듀얼 검증 및 FO 화면 내 바운딩박스 인라인 교정 UI 제공</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>그룹 보안심의 대기로 인한 외부 OCR/LLM API 방화벽 오픈 지연 위험</t>
+          <t>그룹 보안검토 대기로 인한 외부 OCR/LLM API 방화벽 오픈 지연 위험</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>미출시 신제품 전성분 배합비가 외부 LLM API로 전송될 보안 위험</t>
+          <t>미출시 신제품 자재BOM 조성비가 외부 LLM API로 전송될 보안 위험</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>전성분 배합 한도 대조는 내부 DB SQL/정규식(1단계)에서만 처리하고 LLM에는 판정 플래그만 전달</t>
+          <t>자재BOM 조성 한도 대조는 내부 DB SQL/정규식(1단계)에서만 처리하고 LLM에는 판정 플래그만 전달</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>식약처 고시 개정에 따른 신규 규제 룰셋 수시 추가 요청 위험</t>
+          <t>공정위·표준원 고시 개정에 따른 신규 규제 룰셋 수시 추가 요청 위험</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
